--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6891268-0FF3-AE4E-B2EB-ACA109EB417F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03156791-B650-F940-B641-2478384906A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1200" yWindow="3040" windowWidth="26800" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -308,65 +308,80 @@
     <t>internal</t>
   </si>
   <si>
-    <t>mid</t>
-  </si>
-  <si>
-    <t>chainstay.h</t>
-  </si>
-  <si>
-    <t>frontcenter.h</t>
-  </si>
-  <si>
     <t>alpha</t>
   </si>
   <si>
     <t>offset</t>
   </si>
   <si>
-    <t>HTA rad</t>
-  </si>
-  <si>
-    <t>ac</t>
-  </si>
-  <si>
     <t>beta</t>
   </si>
   <si>
     <t>ac.v</t>
   </si>
   <si>
-    <t>beta deg</t>
-  </si>
-  <si>
     <t>h.v</t>
   </si>
   <si>
     <t>ht length</t>
   </si>
   <si>
-    <t>crown race</t>
-  </si>
-  <si>
-    <t>HT length</t>
-  </si>
-  <si>
-    <t>chainstay mid</t>
-  </si>
-  <si>
-    <t>wheelbase mid</t>
-  </si>
-  <si>
     <t>wheelbase.mid</t>
   </si>
   <si>
     <t>a8:f31</t>
+  </si>
+  <si>
+    <t>bb drop</t>
+  </si>
+  <si>
+    <t>hta</t>
+  </si>
+  <si>
+    <t>axle-crown</t>
+  </si>
+  <si>
+    <t>crown-race</t>
+  </si>
+  <si>
+    <t>hta rad</t>
+  </si>
+  <si>
+    <t>crown-race.v</t>
+  </si>
+  <si>
+    <t>bike geometry goodnotes</t>
+  </si>
+  <si>
+    <t>delta</t>
+  </si>
+  <si>
+    <t>gamma</t>
+  </si>
+  <si>
+    <t>chainstay</t>
+  </si>
+  <si>
+    <t>steer_axis_v</t>
+  </si>
+  <si>
+    <t>steer_axis_h</t>
+  </si>
+  <si>
+    <t>rc.h</t>
+  </si>
+  <si>
+    <t>offset_h</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.00000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -377,6 +392,11 @@
       <color rgb="FF000000"/>
       <name val="Futura"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Futura Medium"/>
     </font>
   </fonts>
   <fills count="2">
@@ -399,11 +419,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -700,13 +722,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M71"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -714,7 +736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -722,7 +744,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -730,7 +752,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -738,7 +760,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -746,15 +768,15 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -774,7 +796,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -793,8 +815,34 @@
       <c r="F9">
         <v>422</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9">
+        <f>C10</f>
+        <v>586</v>
+      </c>
+      <c r="J9">
+        <f t="shared" ref="J9:L9" si="0">D10</f>
+        <v>609</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="0"/>
+        <v>630</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="0"/>
+        <v>651</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9">
+        <f>C10</f>
+        <v>586</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -813,8 +861,34 @@
       <c r="F10">
         <v>651</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="I10">
+        <f>C12</f>
+        <v>70</v>
+      </c>
+      <c r="J10">
+        <f t="shared" ref="J10:L10" si="1">D12</f>
+        <v>70</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="1"/>
+        <v>70</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O10">
+        <f>C9</f>
+        <v>370</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -833,8 +907,34 @@
       <c r="F11">
         <v>70.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <f>C11</f>
+        <v>70</v>
+      </c>
+      <c r="J11">
+        <f t="shared" ref="J11:L11" si="2">D11</f>
+        <v>70.5</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="2"/>
+        <v>70.5</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>70.5</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="O11">
+        <f>C12</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -853,10 +953,36 @@
       <c r="F12">
         <v>70</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12">
+        <f>C21</f>
+        <v>415</v>
+      </c>
+      <c r="J12">
+        <f t="shared" ref="J12:L12" si="3">D21</f>
+        <v>415</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="3"/>
+        <v>415</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="3"/>
+        <v>415</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="O12">
+        <f>C11</f>
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -873,8 +999,34 @@
       <c r="F13">
         <v>1097</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I13">
+        <f>C20</f>
+        <v>50</v>
+      </c>
+      <c r="J13">
+        <f t="shared" ref="J13:L13" si="4">D20</f>
+        <v>50</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="4"/>
+        <v>50</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="O13">
+        <f>C14</f>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -893,8 +1045,30 @@
       <c r="F14">
         <v>412</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I14" s="1">
+        <v>10</v>
+      </c>
+      <c r="J14" s="1">
+        <v>11</v>
+      </c>
+      <c r="K14" s="1">
+        <v>12</v>
+      </c>
+      <c r="L14" s="1">
+        <v>13</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O14">
+        <f>C13</f>
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -913,8 +1087,15 @@
       <c r="F15">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="N15" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="O15">
+        <f>C21</f>
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -922,23 +1103,49 @@
         <v>29</v>
       </c>
       <c r="C16" s="3">
-        <f>I37</f>
-        <v>145.16322723728678</v>
+        <f>I22</f>
+        <v>145.16322723728675</v>
       </c>
       <c r="D16" s="3">
-        <f>J37</f>
-        <v>167.35589931404664</v>
+        <f t="shared" ref="D16:F16" si="5">J22</f>
+        <v>166.35589931404667</v>
       </c>
       <c r="E16" s="3">
-        <f>K37</f>
-        <v>189.63372200533158</v>
+        <f t="shared" si="5"/>
+        <v>187.63372200533158</v>
       </c>
       <c r="F16" s="3">
-        <f>L37</f>
-        <v>211.91154469661652</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="5"/>
+        <v>208.91154469661646</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16">
+        <f>I11*PI()/180</f>
+        <v>1.2217304763960306</v>
+      </c>
+      <c r="J16">
+        <f t="shared" ref="J16:L16" si="6">J11*PI()/180</f>
+        <v>1.2304571226560022</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="6"/>
+        <v>1.2304571226560022</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="6"/>
+        <v>1.2304571226560022</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O16">
+        <f>C20</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -947,35 +1154,107 @@
         <v>1020</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" ref="D17:F17" si="0">D13-9</f>
+        <f t="shared" ref="D17:F17" si="7">D13-9</f>
         <v>1035</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1062</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="7"/>
         <v>1088</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="I17">
+        <f>I14*SIN(I16)</f>
+        <v>9.3969262078590834</v>
+      </c>
+      <c r="J17">
+        <f t="shared" ref="J17:L17" si="8">J14*SIN(J16)</f>
+        <v>10.369056402013962</v>
+      </c>
+      <c r="K17">
+        <f t="shared" si="8"/>
+        <v>11.311697893106139</v>
+      </c>
+      <c r="L17">
+        <f t="shared" si="8"/>
+        <v>12.254339384198317</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H18" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="I18">
+        <f>ATAN(I13/I12)</f>
+        <v>0.1199039853650239</v>
+      </c>
+      <c r="J18">
+        <f t="shared" ref="J18:L18" si="9">ATAN(J13/J12)</f>
+        <v>0.1199039853650239</v>
+      </c>
+      <c r="K18">
+        <f t="shared" si="9"/>
+        <v>0.1199039853650239</v>
+      </c>
+      <c r="L18">
+        <f t="shared" si="9"/>
+        <v>0.1199039853650239</v>
+      </c>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H19" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19">
+        <f>I18 + ( PI()/2 - I16)</f>
+        <v>0.46896983576388984</v>
+      </c>
+      <c r="J19">
+        <f t="shared" ref="J19:L19" si="10">J18 + ( PI()/2 - J16)</f>
+        <v>0.46024318950391829</v>
+      </c>
+      <c r="K19">
+        <f t="shared" si="10"/>
+        <v>0.46024318950391829</v>
+      </c>
+      <c r="L19">
+        <f t="shared" si="10"/>
+        <v>0.46024318950391829</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="O19">
+        <f>O12*PI()/180</f>
+        <v>1.2217304763960306</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -997,8 +1276,34 @@
       <c r="G20" s="1" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20">
+        <f>COS(I19)*I12</f>
+        <v>370.19426034779457</v>
+      </c>
+      <c r="J20">
+        <f t="shared" ref="J20:L20" si="11">COS(J19)*J12</f>
+        <v>371.81697061661282</v>
+      </c>
+      <c r="K20">
+        <f t="shared" si="11"/>
+        <v>371.81697061661282</v>
+      </c>
+      <c r="L20">
+        <f t="shared" si="11"/>
+        <v>371.81697061661282</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="O20">
+        <f>O17*SIN(O19)</f>
+        <v>9.3969262078590834</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -1017,23 +1322,34 @@
       <c r="F21">
         <v>415</v>
       </c>
-      <c r="H21" t="s">
-        <v>22</v>
+      <c r="H21" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="I21">
-        <v>70</v>
+        <f>I9-I10-I17-I20</f>
+        <v>136.40881344434632</v>
       </c>
       <c r="J21">
-        <v>70</v>
+        <f t="shared" ref="J21:L21" si="12">J9-J10-J17-J20</f>
+        <v>156.81397298137324</v>
       </c>
       <c r="K21">
-        <v>70</v>
+        <f t="shared" si="12"/>
+        <v>176.87133149028102</v>
       </c>
       <c r="L21">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="12"/>
+        <v>196.9286899991888</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="O21" s="4">
+        <f>O9-O11</f>
+        <v>516</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1041,51 +1357,50 @@
         <v>34</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="I22">
-        <v>421</v>
+        <f>I21/SIN(I16)</f>
+        <v>145.16322723728675</v>
       </c>
       <c r="J22">
-        <v>421</v>
+        <f t="shared" ref="J22:L22" si="13">J21/SIN(J16)</f>
+        <v>166.35589931404667</v>
       </c>
       <c r="K22">
-        <v>421</v>
+        <f t="shared" si="13"/>
+        <v>187.63372200533158</v>
       </c>
       <c r="L22">
-        <v>421</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="13"/>
+        <v>208.91154469661646</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="O22">
+        <f>O21/TAN(O19)</f>
+        <v>187.8086408813605</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I23">
-        <v>1029</v>
-      </c>
-      <c r="J23">
-        <v>1044</v>
-      </c>
-      <c r="K23">
-        <v>1071</v>
-      </c>
-      <c r="L23">
-        <v>1097</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="M23" s="1"/>
+      <c r="N23" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="O23">
+        <f>SQRT(O13^2 - O11^2)</f>
+        <v>406.00985209721205</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1093,26 +1408,17 @@
         <v>36</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="I24">
-        <f>SQRT(I22^2 -I21^2)</f>
-        <v>415.13973551082773</v>
-      </c>
-      <c r="J24">
-        <f t="shared" ref="J24:L24" si="1">SQRT(J22^2 -J21^2)</f>
-        <v>415.13973551082773</v>
-      </c>
-      <c r="K24">
-        <f t="shared" si="1"/>
-        <v>415.13973551082773</v>
-      </c>
-      <c r="L24">
-        <f t="shared" si="1"/>
-        <v>415.13973551082773</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="O24">
+        <f>O14-O23-O10-O22</f>
+        <v>65.18150702142745</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1123,28 +1429,54 @@
         <v>93</v>
       </c>
       <c r="I25">
-        <f>I23-I24</f>
-        <v>613.86026448917232</v>
+        <f>ACOS(I13/I12)</f>
+        <v>1.4500209946179365</v>
       </c>
       <c r="J25">
-        <f t="shared" ref="J25:L25" si="2">J23-J24</f>
-        <v>628.86026448917232</v>
+        <f t="shared" ref="J25:L25" si="14">ACOS(J13/J12)</f>
+        <v>1.4500209946179365</v>
       </c>
       <c r="K25">
-        <f t="shared" si="2"/>
-        <v>655.86026448917232</v>
+        <f t="shared" si="14"/>
+        <v>1.4500209946179365</v>
       </c>
       <c r="L25">
-        <f t="shared" si="2"/>
-        <v>681.86026448917232</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="14"/>
+        <v>1.4500209946179365</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="O25">
+        <f>O24*SIN(O19)</f>
+        <v>61.250581159740243</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="H26" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="I26">
+        <f>PI()/2 - I16</f>
+        <v>0.34906585039886595</v>
+      </c>
+      <c r="J26">
+        <f t="shared" ref="J26:L26" si="15">PI()/2 - J16</f>
+        <v>0.3403392041388944</v>
+      </c>
+      <c r="K26">
+        <f t="shared" si="15"/>
+        <v>0.3403392041388944</v>
+      </c>
+      <c r="L26">
+        <f t="shared" si="15"/>
+        <v>0.3403392041388944</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1164,26 +1496,28 @@
         <v>700</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" s="1">
-        <f>C11*PI()/180</f>
-        <v>1.2217304763960306</v>
-      </c>
-      <c r="J27" s="1">
-        <f>D11*PI()/180</f>
-        <v>1.2304571226560022</v>
-      </c>
-      <c r="K27" s="1">
-        <f>E11*PI()/180</f>
-        <v>1.2304571226560022</v>
-      </c>
-      <c r="L27" s="1">
-        <f>F11*PI()/180</f>
-        <v>1.2304571226560022</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+      <c r="I27">
+        <f>I25-I26</f>
+        <v>1.1009551442190706</v>
+      </c>
+      <c r="J27">
+        <f t="shared" ref="J27:L27" si="16">J25-J26</f>
+        <v>1.1096817904790421</v>
+      </c>
+      <c r="K27">
+        <f t="shared" si="16"/>
+        <v>1.1096817904790421</v>
+      </c>
+      <c r="L27">
+        <f t="shared" si="16"/>
+        <v>1.1096817904790421</v>
+      </c>
+      <c r="N27" s="5"/>
+      <c r="O27" s="5"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1203,26 +1537,28 @@
         <v>50</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I28">
-        <f t="shared" ref="I28:L29" si="3">C20</f>
-        <v>50</v>
+        <f>I12*SIN(I27)</f>
+        <v>370.03068432148956</v>
       </c>
       <c r="J28">
-        <f t="shared" si="3"/>
-        <v>50</v>
+        <f t="shared" ref="J28:L28" si="17">J12*SIN(J27)</f>
+        <v>371.65621509456895</v>
       </c>
       <c r="K28">
-        <f t="shared" si="3"/>
-        <v>50</v>
+        <f t="shared" si="17"/>
+        <v>371.65621509456895</v>
       </c>
       <c r="L28">
-        <f t="shared" si="3"/>
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="17"/>
+        <v>371.65621509456895</v>
+      </c>
+      <c r="N28" s="5"/>
+      <c r="O28" s="5"/>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1242,243 +1578,176 @@
         <v>56</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I29">
-        <f t="shared" si="3"/>
-        <v>415</v>
+        <f>I9-I28-I17-I10</f>
+        <v>136.57238947065136</v>
       </c>
       <c r="J29">
-        <f t="shared" si="3"/>
-        <v>415</v>
+        <f t="shared" ref="J29:L29" si="18">J9-J28-J17-J10</f>
+        <v>156.97472850341708</v>
       </c>
       <c r="K29">
-        <f t="shared" si="3"/>
-        <v>415</v>
+        <f t="shared" si="18"/>
+        <v>177.03208701232492</v>
       </c>
       <c r="L29">
-        <f t="shared" si="3"/>
-        <v>415</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+        <f t="shared" si="18"/>
+        <v>197.08944552123273</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="O29">
+        <f>ATAN(O16/O15)</f>
+        <v>0.1199039853650239</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>42</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I30" s="1">
-        <f>ATAN(I28/I29)</f>
-        <v>0.1199039853650239</v>
-      </c>
-      <c r="J30" s="1">
-        <f t="shared" ref="J30:L30" si="4">ATAN(J28/J29)</f>
-        <v>0.1199039853650239</v>
-      </c>
-      <c r="K30" s="1">
-        <f t="shared" si="4"/>
-        <v>0.1199039853650239</v>
-      </c>
-      <c r="L30" s="1">
-        <f t="shared" si="4"/>
-        <v>0.1199039853650239</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+      <c r="I30">
+        <f>I29/SIN(I16)</f>
+        <v>145.3373012085905</v>
+      </c>
+      <c r="J30">
+        <f t="shared" ref="J30:L30" si="19">J29/SIN(J16)</f>
+        <v>166.52643660055799</v>
+      </c>
+      <c r="K30">
+        <f t="shared" si="19"/>
+        <v>187.80425929184295</v>
+      </c>
+      <c r="L30">
+        <f t="shared" si="19"/>
+        <v>209.08208198312786</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O30">
+        <f>O29 + ( PI()/2 - O19)</f>
+        <v>0.46896983576388984</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>43</v>
       </c>
-      <c r="H31" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I31">
-        <f>I30 + (PI()/2 - I27)</f>
-        <v>0.46896983576388984</v>
-      </c>
-      <c r="J31">
-        <f t="shared" ref="J31:L31" si="5">J30 + (PI()/2 - J27)</f>
-        <v>0.46024318950391829</v>
-      </c>
-      <c r="K31">
-        <f t="shared" si="5"/>
-        <v>0.46024318950391829</v>
-      </c>
-      <c r="L31">
-        <f t="shared" si="5"/>
-        <v>0.46024318950391829</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="H32" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="I32">
-        <f>I31*180/PI()</f>
-        <v>26.869992308214261</v>
-      </c>
-      <c r="J32">
-        <f t="shared" ref="J32:L32" si="6">J31*180/PI()</f>
-        <v>26.369992308214268</v>
-      </c>
-      <c r="K32">
-        <f t="shared" si="6"/>
-        <v>26.369992308214268</v>
-      </c>
-      <c r="L32">
-        <f t="shared" si="6"/>
-        <v>26.369992308214268</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N31" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O31">
+        <f>COS(O30)*O15</f>
+        <v>370.19426034779457</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="N32" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O32">
+        <f>O9-O11-O20-O31</f>
+        <v>136.40881344434632</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>44</v>
       </c>
       <c r="B33" t="s">
         <v>45</v>
       </c>
-      <c r="H33" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I33">
-        <f>COS(I31)*I29</f>
-        <v>370.19426034779457</v>
-      </c>
-      <c r="J33">
-        <f t="shared" ref="J33:L33" si="7">COS(J31)*J29</f>
-        <v>371.81697061661282</v>
-      </c>
-      <c r="K33">
-        <f t="shared" si="7"/>
-        <v>371.81697061661282</v>
-      </c>
-      <c r="L33">
-        <f t="shared" si="7"/>
-        <v>371.81697061661282</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H33" s="1"/>
+      <c r="N33" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O33">
+        <f>O32/SIN(O19)</f>
+        <v>145.16322723728675</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>82</v>
       </c>
       <c r="B34" t="s">
         <v>83</v>
       </c>
-      <c r="H34" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I34">
-        <f>C10-I33-I21</f>
-        <v>145.80573965220543</v>
-      </c>
-      <c r="J34">
-        <f t="shared" ref="J34:L34" si="8">D10-J33-J21</f>
-        <v>167.18302938338718</v>
-      </c>
-      <c r="K34">
-        <f t="shared" si="8"/>
-        <v>188.18302938338718</v>
-      </c>
-      <c r="L34">
-        <f t="shared" si="8"/>
-        <v>209.18302938338718</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H34" s="1"/>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>84</v>
       </c>
       <c r="B35" t="s">
         <v>85</v>
       </c>
-      <c r="H35" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="I35">
-        <f>I34/SIN(I27)</f>
-        <v>155.16322723728678</v>
-      </c>
-      <c r="J35">
-        <f>J34/SIN(J27)</f>
-        <v>177.35589931404664</v>
-      </c>
-      <c r="K35">
-        <f>K34/SIN(K27)</f>
-        <v>199.63372200533158</v>
-      </c>
-      <c r="L35">
-        <f>L34/SIN(L27)</f>
-        <v>221.91154469661652</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="N35" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>86</v>
       </c>
       <c r="B36" t="s">
         <v>87</v>
       </c>
-      <c r="H36" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I36">
-        <v>10</v>
-      </c>
-      <c r="J36">
-        <v>10</v>
-      </c>
-      <c r="K36">
-        <v>10</v>
-      </c>
-      <c r="L36">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H36" s="1"/>
+      <c r="N36" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="O36">
+        <f>ACOS(O16/O15)</f>
+        <v>1.4500209946179365</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>46</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
       </c>
-      <c r="H37" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="I37" s="3">
-        <f>I35-I36</f>
-        <v>145.16322723728678</v>
-      </c>
-      <c r="J37" s="3">
-        <f>J35-J36</f>
-        <v>167.35589931404664</v>
-      </c>
-      <c r="K37" s="3">
-        <f>K35-K36</f>
-        <v>189.63372200533158</v>
-      </c>
-      <c r="L37" s="3">
-        <f>L35-L36</f>
-        <v>211.91154469661652</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H37" s="1"/>
+      <c r="N37" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="O37">
+        <f>PI()/2 - O19</f>
+        <v>0.34906585039886595</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>48</v>
       </c>
-      <c r="I38">
-        <v>145</v>
-      </c>
-      <c r="J38">
-        <v>167</v>
-      </c>
-      <c r="K38">
-        <v>190</v>
-      </c>
-      <c r="L38">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H38" s="1"/>
+      <c r="N38" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="O38">
+        <f>O36-O37</f>
+        <v>1.1009551442190706</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>49</v>
       </c>
@@ -1486,51 +1755,80 @@
         <v>18</v>
       </c>
       <c r="H39" s="1"/>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="N39" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="O39">
+        <f>O15*SIN(O38)</f>
+        <v>370.03068432148956</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>50</v>
       </c>
       <c r="B40">
         <v>56</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H40" s="1"/>
+      <c r="N40" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O40">
+        <f>O9-O39-O20-O11</f>
+        <v>136.57238947065136</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H41" s="1"/>
+      <c r="N41" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="O41">
+        <f>O40/SIN(O19)</f>
+        <v>145.3373012085905</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H42" s="1"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="K42" s="3"/>
+      <c r="L42" s="3"/>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H44" s="1"/>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>58</v>
       </c>

--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03156791-B650-F940-B641-2478384906A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C5610C-9E7A-1941-99CB-7863F6837BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1200" yWindow="3040" windowWidth="26800" windowHeight="14280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-22400" windowWidth="30280" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>brand</t>
   </si>
@@ -326,9 +326,6 @@
     <t>ht length</t>
   </si>
   <si>
-    <t>wheelbase.mid</t>
-  </si>
-  <si>
     <t>a8:f31</t>
   </si>
   <si>
@@ -372,6 +369,54 @@
   </si>
   <si>
     <t>offset_h</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>Hi Jeff!</t>
+  </si>
+  <si>
+    <t>Pulled together some numbers for you</t>
+  </si>
+  <si>
+    <t>1. $5800 is for a simple, high quality full build featuring companies like I9, whiskey and Sram</t>
+  </si>
+  <si>
+    <t>2. Yes! We design around a ~410mm fork length, which is comfortably in the gravel/MCX world</t>
+  </si>
+  <si>
+    <t>3. Wheelbase on the geometry chart WAS around the longest rocker position, I've modified it so it now shows the full range (thank you for that)</t>
+  </si>
+  <si>
+    <t>S 1011-1029    M 1026-1044    L 1053-1071    XL 1079-1097</t>
+  </si>
+  <si>
+    <t>4. Headtube lengths: S 145mm  M 165mm  L 185mm  XL 205mm</t>
+  </si>
+  <si>
+    <t>Seat tube lengths: S 470  M 540  L 565  XL 580 </t>
+  </si>
+  <si>
+    <t>Due to the lack of an XS frame, we designed the seat tube shorter in the small size to allow use of a dropper post. The standover height between sizes remains fairly linear. </t>
+  </si>
+  <si>
+    <t>Thanks for your interest in Solace! </t>
+  </si>
+  <si>
+    <t>Please reach out with any more design questions or any thoughts at all!</t>
+  </si>
+  <si>
+    <t>(We love to talk about bikes and ourselves )</t>
+  </si>
+  <si>
+    <t>-- </t>
+  </si>
+  <si>
+    <t>Tyler Kepes</t>
+  </si>
+  <si>
+    <t>wheelbase.long (see email)</t>
   </si>
 </sst>
 </file>
@@ -381,7 +426,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color rgb="FF000000"/>
@@ -397,6 +442,12 @@
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Futura Medium"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF888888"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -419,13 +470,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -441,6 +493,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -722,13 +778,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:T71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -736,7 +792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -744,7 +800,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -752,7 +808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -760,7 +816,7 @@
         <v>45920</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -768,15 +824,29 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <v>1011</v>
+      </c>
+      <c r="R6">
+        <v>1026</v>
+      </c>
+      <c r="S6">
+        <v>1053</v>
+      </c>
+      <c r="T6">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -796,7 +866,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>15</v>
       </c>
@@ -841,8 +911,11 @@
         <f>C10</f>
         <v>586</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -862,7 +935,7 @@
         <v>651</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I10">
         <f>C12</f>
@@ -888,7 +961,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -908,7 +981,7 @@
         <v>70.5</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I11">
         <f>C11</f>
@@ -927,14 +1000,17 @@
         <v>70.5</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O11">
         <f>C12</f>
         <v>70</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q11" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -954,7 +1030,7 @@
         <v>70</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I12">
         <f>C21</f>
@@ -973,16 +1049,16 @@
         <v>415</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O12">
         <f>C11</f>
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B13" t="s">
         <v>24</v>
@@ -1019,14 +1095,17 @@
         <v>50</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="O13">
         <f>C14</f>
         <v>412</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q13" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -1046,7 +1125,7 @@
         <v>412</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I14" s="1">
         <v>10</v>
@@ -1068,7 +1147,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>27</v>
       </c>
@@ -1088,14 +1167,17 @@
         <v>73</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <f>C21</f>
         <v>415</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q15" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>29</v>
       </c>
@@ -1107,34 +1189,34 @@
         <v>145.16322723728675</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" ref="D16:F16" si="5">J22</f>
-        <v>166.35589931404667</v>
+        <v>165</v>
       </c>
       <c r="E16" s="3">
-        <f t="shared" si="5"/>
-        <v>187.63372200533158</v>
+        <v>185</v>
       </c>
       <c r="F16" s="3">
-        <f t="shared" si="5"/>
-        <v>208.91154469661646</v>
+        <v>205</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="I16">
         <f>I11*PI()/180</f>
         <v>1.2217304763960306</v>
       </c>
       <c r="J16">
-        <f t="shared" ref="J16:L16" si="6">J11*PI()/180</f>
+        <f t="shared" ref="J16:L16" si="5">J11*PI()/180</f>
         <v>1.2304571226560022</v>
       </c>
       <c r="K16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2304571226560022</v>
       </c>
       <c r="L16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>1.2304571226560022</v>
       </c>
       <c r="N16" s="1" t="s">
@@ -1145,58 +1227,76 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
       <c r="C17" s="3">
-        <f>C13-9</f>
-        <v>1020</v>
+        <f>C13-18</f>
+        <v>1011</v>
       </c>
       <c r="D17" s="3">
-        <f t="shared" ref="D17:F17" si="7">D13-9</f>
-        <v>1035</v>
+        <f t="shared" ref="D17:F17" si="6">D13-18</f>
+        <v>1026</v>
       </c>
       <c r="E17" s="3">
-        <f t="shared" si="7"/>
-        <v>1062</v>
+        <f t="shared" si="6"/>
+        <v>1053</v>
       </c>
       <c r="F17" s="3">
-        <f t="shared" si="7"/>
-        <v>1088</v>
+        <f t="shared" si="6"/>
+        <v>1079</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I17">
         <f>I14*SIN(I16)</f>
         <v>9.3969262078590834</v>
       </c>
       <c r="J17">
-        <f t="shared" ref="J17:L17" si="8">J14*SIN(J16)</f>
+        <f t="shared" ref="J17:L17" si="7">J14*SIN(J16)</f>
         <v>10.369056402013962</v>
       </c>
       <c r="K17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>11.311697893106139</v>
       </c>
       <c r="L17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>12.254339384198317</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O17" s="1">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q17" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" t="s">
         <v>30</v>
+      </c>
+      <c r="C18">
+        <v>470</v>
+      </c>
+      <c r="D18">
+        <v>540</v>
+      </c>
+      <c r="E18">
+        <v>565</v>
+      </c>
+      <c r="F18">
+        <v>580</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>91</v>
@@ -1206,21 +1306,24 @@
         <v>0.1199039853650239</v>
       </c>
       <c r="J18">
-        <f t="shared" ref="J18:L18" si="9">ATAN(J13/J12)</f>
+        <f t="shared" ref="J18:L18" si="8">ATAN(J13/J12)</f>
         <v>0.1199039853650239</v>
       </c>
       <c r="K18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1199039853650239</v>
       </c>
       <c r="L18">
-        <f t="shared" si="9"/>
+        <f t="shared" si="8"/>
         <v>0.1199039853650239</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q18" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
@@ -1235,26 +1338,26 @@
         <v>0.46896983576388984</v>
       </c>
       <c r="J19">
-        <f t="shared" ref="J19:L19" si="10">J18 + ( PI()/2 - J16)</f>
+        <f t="shared" ref="J19:L19" si="9">J18 + ( PI()/2 - J16)</f>
         <v>0.46024318950391829</v>
       </c>
       <c r="K19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.46024318950391829</v>
       </c>
       <c r="L19">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.46024318950391829</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="O19">
         <f>O12*PI()/180</f>
         <v>1.2217304763960306</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1284,26 +1387,29 @@
         <v>370.19426034779457</v>
       </c>
       <c r="J20">
-        <f t="shared" ref="J20:L20" si="11">COS(J19)*J12</f>
+        <f t="shared" ref="J20:L20" si="10">COS(J19)*J12</f>
         <v>371.81697061661282</v>
       </c>
       <c r="K20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>371.81697061661282</v>
       </c>
       <c r="L20">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>371.81697061661282</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O20">
         <f>O17*SIN(O19)</f>
         <v>9.3969262078590834</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q20" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>33</v>
       </c>
@@ -1330,26 +1436,29 @@
         <v>136.40881344434632</v>
       </c>
       <c r="J21">
-        <f t="shared" ref="J21:L21" si="12">J9-J10-J17-J20</f>
+        <f t="shared" ref="J21:L21" si="11">J9-J10-J17-J20</f>
         <v>156.81397298137324</v>
       </c>
       <c r="K21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>176.87133149028102</v>
       </c>
       <c r="L21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="11"/>
         <v>196.9286899991888</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O21" s="4">
         <f>O9-O11</f>
         <v>516</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q21" s="1" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>34</v>
       </c>
@@ -1364,27 +1473,27 @@
         <v>145.16322723728675</v>
       </c>
       <c r="J22">
-        <f t="shared" ref="J22:L22" si="13">J21/SIN(J16)</f>
+        <f t="shared" ref="J22:L22" si="12">J21/SIN(J16)</f>
         <v>166.35589931404667</v>
       </c>
       <c r="K22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>187.63372200533158</v>
       </c>
       <c r="L22">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>208.91154469661646</v>
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="O22">
         <f>O21/TAN(O19)</f>
         <v>187.8086408813605</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1393,14 +1502,17 @@
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O23">
         <f>SQRT(O13^2 - O11^2)</f>
         <v>406.00985209721205</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q23" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>36</v>
       </c>
@@ -1408,17 +1520,17 @@
         <v>36</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="O24">
         <f>O14-O23-O10-O22</f>
         <v>65.18150702142745</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>37</v>
       </c>
@@ -1433,15 +1545,15 @@
         <v>1.4500209946179365</v>
       </c>
       <c r="J25">
-        <f t="shared" ref="J25:L25" si="14">ACOS(J13/J12)</f>
+        <f t="shared" ref="J25:L25" si="13">ACOS(J13/J12)</f>
         <v>1.4500209946179365</v>
       </c>
       <c r="K25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.4500209946179365</v>
       </c>
       <c r="L25">
-        <f t="shared" si="14"/>
+        <f t="shared" si="13"/>
         <v>1.4500209946179365</v>
       </c>
       <c r="N25" s="1" t="s">
@@ -1451,32 +1563,35 @@
         <f>O24*SIN(O19)</f>
         <v>61.250581159740243</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q25" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>38</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I26">
         <f>PI()/2 - I16</f>
         <v>0.34906585039886595</v>
       </c>
       <c r="J26">
-        <f t="shared" ref="J26:L26" si="15">PI()/2 - J16</f>
+        <f t="shared" ref="J26:L26" si="14">PI()/2 - J16</f>
         <v>0.3403392041388944</v>
       </c>
       <c r="K26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.3403392041388944</v>
       </c>
       <c r="L26">
-        <f t="shared" si="15"/>
+        <f t="shared" si="14"/>
         <v>0.3403392041388944</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>39</v>
       </c>
@@ -1496,28 +1611,31 @@
         <v>700</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="I27">
         <f>I25-I26</f>
         <v>1.1009551442190706</v>
       </c>
       <c r="J27">
-        <f t="shared" ref="J27:L27" si="16">J25-J26</f>
+        <f t="shared" ref="J27:L27" si="15">J25-J26</f>
         <v>1.1096817904790421</v>
       </c>
       <c r="K27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.1096817904790421</v>
       </c>
       <c r="L27">
-        <f t="shared" si="16"/>
+        <f t="shared" si="15"/>
         <v>1.1096817904790421</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5"/>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q27" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>40</v>
       </c>
@@ -1544,21 +1662,24 @@
         <v>370.03068432148956</v>
       </c>
       <c r="J28">
-        <f t="shared" ref="J28:L28" si="17">J12*SIN(J27)</f>
+        <f t="shared" ref="J28:L28" si="16">J12*SIN(J27)</f>
         <v>371.65621509456895</v>
       </c>
       <c r="K28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>371.65621509456895</v>
       </c>
       <c r="L28">
-        <f t="shared" si="17"/>
+        <f t="shared" si="16"/>
         <v>371.65621509456895</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5"/>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q28" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>41</v>
       </c>
@@ -1585,15 +1706,15 @@
         <v>136.57238947065136</v>
       </c>
       <c r="J29">
-        <f t="shared" ref="J29:L29" si="18">J9-J28-J17-J10</f>
+        <f t="shared" ref="J29:L29" si="17">J9-J28-J17-J10</f>
         <v>156.97472850341708</v>
       </c>
       <c r="K29">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>177.03208701232492</v>
       </c>
       <c r="L29">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>197.08944552123273</v>
       </c>
       <c r="N29" s="1" t="s">
@@ -1604,7 +1725,7 @@
         <v>0.1199039853650239</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>42</v>
       </c>
@@ -1616,15 +1737,15 @@
         <v>145.3373012085905</v>
       </c>
       <c r="J30">
-        <f t="shared" ref="J30:L30" si="19">J29/SIN(J16)</f>
+        <f t="shared" ref="J30:L30" si="18">J29/SIN(J16)</f>
         <v>166.52643660055799</v>
       </c>
       <c r="K30">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>187.80425929184295</v>
       </c>
       <c r="L30">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>209.08208198312786</v>
       </c>
       <c r="N30" s="1" t="s">
@@ -1634,8 +1755,11 @@
         <f>O29 + ( PI()/2 - O19)</f>
         <v>0.46896983576388984</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q30" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>43</v>
       </c>
@@ -1646,8 +1770,11 @@
         <f>COS(O30)*O15</f>
         <v>370.19426034779457</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q31" s="6" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
@@ -1699,7 +1826,7 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="N35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -1727,7 +1854,7 @@
       </c>
       <c r="H37" s="1"/>
       <c r="N37" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O37">
         <f>PI()/2 - O19</f>
@@ -1740,7 +1867,7 @@
       </c>
       <c r="H38" s="1"/>
       <c r="N38" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="O38">
         <f>O36-O37</f>

--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7C5610C-9E7A-1941-99CB-7863F6837BDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8483BB-CCAC-DB4B-8A71-35031CEE56BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-22400" windowWidth="30280" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>wheelbase.long (see email)</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -493,10 +496,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2049,39 +2048,45 @@
         <v>74</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="B69">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>81</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C8483BB-CCAC-DB4B-8A71-35031CEE56BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F79F3-28A0-A545-8B8C-081B05E1B78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-22400" windowWidth="30280" windowHeight="15300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7800" yWindow="620" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="130">
   <si>
     <t>brand</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://cdn.prod.website-files.com/61d760661f2d63979bdb4b3c/61fc87d2ea6ac83d9ea1e4d0_Hero-Cover-OM3-2x-p-2600.jpeg</t>
   </si>
 </sst>
 </file>
@@ -824,6 +827,9 @@
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
       <c r="Q6">
         <v>1011</v>
       </c>

--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E74F79F3-28A0-A545-8B8C-081B05E1B78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A6E5EC-05DC-1C49-873B-4E9F18004007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7800" yWindow="620" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="132">
   <si>
     <t>brand</t>
   </si>
@@ -423,6 +423,12 @@
   </si>
   <si>
     <t>https://cdn.prod.website-files.com/61d760661f2d63979bdb4b3c/61fc87d2ea6ac83d9ea1e4d0_Hero-Cover-OM3-2x-p-2600.jpeg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Elizabethtown, New York, USA</t>
   </si>
 </sst>
 </file>
@@ -780,7 +786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T71"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -2095,6 +2101,14 @@
         <v>128</v>
       </c>
     </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Solace OM-3 Short 2025.xlsx
+++ b/data/gravel/Solace OM-3 Short 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01A6E5EC-05DC-1C49-873B-4E9F18004007}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00E7E4A0-CC53-F446-AE4A-18CA01E1A396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="138">
   <si>
     <t>brand</t>
   </si>
@@ -429,6 +429,24 @@
   </si>
   <si>
     <t>Elizabethtown, New York, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -786,7 +804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T72"/>
+  <dimension ref="A1:T78"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1968,144 +1986,174 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>58</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>59</v>
+        <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>60</v>
+        <v>134</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>61</v>
+        <v>135</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>63</v>
+        <v>137</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>90</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>73</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>67</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>74</v>
+        <v>68</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B69">
-        <v>5800</v>
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>81</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>128</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
         <v>130</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B78" s="1" t="s">
         <v>131</v>
       </c>
     </row>
